--- a/data/raw/portfolio_snapshots/Portfolio_2024.xlsx
+++ b/data/raw/portfolio_snapshots/Portfolio_2024.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="936" documentId="8_{EDF33660-9B23-4888-B529-2B640994E33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB233030-82C4-4F3A-BAEB-D022E591D20A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="12" activeTab="17" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="17" activeTab="17" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
   </bookViews>
   <sheets>
     <sheet name="01Jan24" sheetId="30" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <sheet name="31stDec24" sheetId="49" r:id="rId21"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId22"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -80,6 +80,9 @@
     <t>Change</t>
   </si>
   <si>
+    <t>AstraMicro</t>
+  </si>
+  <si>
     <t>Heritage</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
     <t>SuryaRosni</t>
   </si>
   <si>
+    <t>ThomasCook</t>
+  </si>
+  <si>
     <t>TIIndia</t>
   </si>
   <si>
@@ -110,58 +116,13 @@
     <t>VRLLogistics</t>
   </si>
   <si>
-    <t>LiquidBees</t>
-  </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
-  <si>
-    <t>AstraMicro</t>
-  </si>
-  <si>
     <t>WelEnt</t>
   </si>
   <si>
     <t>ZenTech</t>
   </si>
   <si>
-    <t>ThomasCook</t>
-  </si>
-  <si>
-    <t>LiquidFund Value for 2024</t>
+    <t>LiquidBees</t>
   </si>
   <si>
     <t>Sell 96@3918.34 = 376160</t>
@@ -191,25 +152,25 @@
     <t>Less 496.76</t>
   </si>
   <si>
-    <t>Less 45@643.63 = 28963</t>
+    <t>Add 3464@157.97 = 547208</t>
   </si>
   <si>
-    <t>Add 3464@157.97 = 547208</t>
+    <t>Less 45@643.63 = 28963</t>
   </si>
   <si>
     <t>Less 518.245</t>
   </si>
   <si>
-    <t>Buy 2345@534.07 = 1252394</t>
+    <t>Buy 135@4691.82 = 633396</t>
   </si>
   <si>
     <t>Buy 1538@146.91 = 225948</t>
   </si>
   <si>
-    <t>Buy 1117@300.66 = 335837</t>
+    <t>Buy 2345@534.07 = 1252394</t>
   </si>
   <si>
-    <t>Buy 135@4691.82 = 633396</t>
+    <t>Buy 1117@300.66 = 335837</t>
   </si>
   <si>
     <t>Less 2447.575</t>
@@ -272,10 +233,10 @@
     <t>Less 3314.616</t>
   </si>
   <si>
-    <t xml:space="preserve">Bonus 1:1 </t>
+    <t>Price as on 18/10/24</t>
   </si>
   <si>
-    <t>Price as on 18/10/24</t>
+    <t xml:space="preserve">Bonus 1:1 </t>
   </si>
   <si>
     <t>Add 2249@470.08 = 1057210</t>
@@ -299,6 +260,45 @@
     <t>Less 1288.599</t>
   </si>
   <si>
+    <t>LiquidFund Value for 2024</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
     <t>Add 99.644</t>
   </si>
 </sst>
@@ -306,7 +306,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,14 +358,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -403,7 +399,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -509,7 +505,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -651,7 +647,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -663,19 +659,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -684,11 +680,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -708,13 +704,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -732,9 +728,9 @@
         <v>8.6206866795462078E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -752,9 +748,9 @@
         <v>4.3315041166930184E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -772,9 +768,9 @@
         <v>3.8668365206874888E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -792,9 +788,9 @@
         <v>4.4705542676157312E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>862+390+71+35-217-171</f>
@@ -812,9 +808,9 @@
         <v>1.7865489961984695E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205</f>
@@ -832,9 +828,9 @@
         <v>5.5812367058372454E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -852,9 +848,9 @@
         <v>0.12308335400645683</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317</f>
@@ -872,9 +868,9 @@
         <v>5.77659753769975E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85</f>
@@ -892,9 +888,9 @@
         <v>4.3499312533629576E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205</f>
@@ -912,9 +908,9 @@
         <v>0.22415604405455763</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -932,9 +928,9 @@
         <v>4.0811908476403029E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459</f>
@@ -952,9 +948,9 @@
         <v>3.9417597362396521E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -972,9 +968,9 @@
         <v>6.2655425230954853E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -992,9 +988,9 @@
         <v>6.6128682566689259E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>48.4+47.4+129.5-97.5-56+86.5+391.64-150.9-44.65+28+666.65-157.4-303.27+183.51-105.34-76.3-98.36+434.72-160.72-64.6+155.95-254.77-161.7-85.65+146.4+135.27+113.1+214.6+13.78-151.45-147.34-70.81-58.76-273.8+189.4+55.07+264.7-276.6-84.36-112.97+24.27-110.22+137.37-247.49+1021.8-192.05+26.325-177.03-179.14-89.792-89.088-97.856+450.59-71.562+397.578+397.301-75.02-22.928-200.46-205.68-43.938-31.811-49.14-46.569-29.16+738.808-401.23-100.49-99.71-232.613+258.656-266.108-170.465+41.913+196.7+377.35+208.038+121.878+28.182-485.27-322.169+668.43-158.668-57.284+224.7-117.369-198.275-129.083-462.433-72.875-123.419-244.78+94.074+103.702-224.999+35.566+48.391-39.24+160.338-155.174+25.14+418.03-263.255-189.24-0.584-4.192-1.638+4.995+35.895+3.597+114.35+45.302-120.94-80.7+72.904-84.743-26.744+218.983-75.256-142.851+0.253+69.61-71.167+30.957+222.439+188.91+72.355-184.538-32.16-119.837-173.096-3.667+2.8606-4.408-0.094+816.414-40.951+314.853-902.092-187.971+1089.576-388.495+905.333-1333.44+246.344+2.976-310+1092.909-498.03+1348.808-852.799-961.499+2.927-60.272-173.975-41.354+10.883-16.86+1119.46-1181.99+37.038+73.378+352.797+997.672-308.837+443.467+711.919+1282.768-2276.683-538.214-548.973+632.774+151.229-61.672+2709.092-582.471-1043.373+1196.928+295.009-904.847+20.192</f>
@@ -1012,11 +1008,11 @@
         <v>5.5908027526133067E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -1035,20 +1031,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1057,11 +1053,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1081,13 +1077,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -1109,9 +1105,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <v>448</v>
@@ -1129,14 +1125,14 @@
       </c>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -1158,9 +1154,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -1182,9 +1178,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -1206,9 +1202,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205+135</f>
@@ -1230,9 +1226,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -1254,9 +1250,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -1278,9 +1274,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -1302,9 +1298,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850</f>
@@ -1326,9 +1322,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -1350,9 +1346,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -1374,9 +1370,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084+1117</f>
@@ -1398,9 +1394,9 @@
       <c r="H17"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -1418,9 +1414,9 @@
         <v>6.6981479903912802E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595</f>
@@ -1438,14 +1434,14 @@
         <v>9.5382227159996891E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -1464,20 +1460,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1485,15 +1481,15 @@
         <v>45447</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1513,13 +1509,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -1541,9 +1537,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <v>448</v>
@@ -1564,9 +1560,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -1588,9 +1584,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -1612,9 +1608,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -1636,9 +1632,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205+135+181</f>
@@ -1657,14 +1653,14 @@
       </c>
       <c r="F10"/>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -1686,9 +1682,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -1710,9 +1706,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -1734,9 +1730,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850</f>
@@ -1758,9 +1754,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -1782,9 +1778,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -1806,9 +1802,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084+1117</f>
@@ -1830,9 +1826,9 @@
       <c r="H17"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -1850,9 +1846,9 @@
         <v>7.128973063606521E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343</f>
@@ -1870,14 +1866,14 @@
         <v>8.3570738217061541E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -1896,20 +1892,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1917,15 +1913,15 @@
         <v>45447</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1945,13 +1941,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -1973,9 +1969,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -1994,14 +1990,14 @@
       </c>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -2023,9 +2019,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -2047,9 +2043,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -2071,9 +2067,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205+135+181</f>
@@ -2095,9 +2091,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -2119,9 +2115,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -2143,9 +2139,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -2167,9 +2163,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850</f>
@@ -2191,9 +2187,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -2215,9 +2211,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -2239,9 +2235,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084+1117</f>
@@ -2263,9 +2259,9 @@
       <c r="H17"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -2283,9 +2279,9 @@
         <v>6.9986396706754286E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343</f>
@@ -2303,11 +2299,11 @@
         <v>8.2042880310403188E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -2326,20 +2322,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2348,11 +2344,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2372,13 +2368,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -2400,9 +2396,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -2424,9 +2420,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -2448,9 +2444,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -2472,9 +2468,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -2496,9 +2492,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205+135+181</f>
@@ -2520,9 +2516,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -2544,9 +2540,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -2568,9 +2564,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -2592,9 +2588,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323</f>
@@ -2613,14 +2609,14 @@
       </c>
       <c r="F14"/>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -2642,9 +2638,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -2666,9 +2662,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084+1117</f>
@@ -2690,9 +2686,9 @@
       <c r="H17"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -2710,9 +2706,9 @@
         <v>9.8668009914839649E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889</f>
@@ -2730,14 +2726,14 @@
         <v>9.5835010493297276E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -2756,20 +2752,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2778,11 +2774,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2802,13 +2798,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -2830,9 +2826,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -2854,9 +2850,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -2878,9 +2874,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -2902,9 +2898,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -2923,14 +2919,14 @@
       </c>
       <c r="F9"/>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205+135+181</f>
@@ -2952,9 +2948,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -2976,9 +2972,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -3000,9 +2996,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -3024,9 +3020,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920</f>
@@ -3045,14 +3041,14 @@
       </c>
       <c r="F14"/>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -3074,9 +3070,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -3098,9 +3094,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084+1117</f>
@@ -3122,9 +3118,9 @@
       <c r="H17"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -3142,9 +3138,9 @@
         <v>0.10085011269057301</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365</f>
@@ -3162,14 +3158,14 @@
         <v>0.12660546410172721</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -3188,20 +3184,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3210,11 +3206,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3234,13 +3230,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -3262,9 +3258,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -3286,9 +3282,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -3310,9 +3306,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -3334,9 +3330,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -3358,9 +3354,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4">
         <v>52890</v>
@@ -3378,14 +3374,14 @@
       </c>
       <c r="F10"/>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>410+205+135+181</f>
@@ -3407,9 +3403,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -3431,9 +3427,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -3455,9 +3451,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -3479,9 +3475,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920</f>
@@ -3503,9 +3499,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4">
         <f>458+115+189</f>
@@ -3527,9 +3523,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -3551,9 +3547,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4">
         <f>7985+1084+1117</f>
@@ -3575,9 +3571,9 @@
       <c r="H18"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4">
         <f>2592+518+820</f>
@@ -3599,9 +3595,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365-3314.616</f>
@@ -3620,12 +3616,12 @@
       </c>
       <c r="F20"/>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21"/>
       <c r="B21" s="4"/>
       <c r="D21"/>
@@ -3635,7 +3631,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22">
@@ -3660,20 +3656,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3681,15 +3677,15 @@
         <v>45573</v>
       </c>
       <c r="D1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3709,13 +3705,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -3737,9 +3733,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -3761,9 +3757,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -3785,9 +3781,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -3809,9 +3805,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -3833,9 +3829,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4">
         <v>52890</v>
@@ -3856,9 +3852,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(410+205+135+181)*2</f>
@@ -3877,14 +3873,14 @@
       </c>
       <c r="F11"/>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -3906,9 +3902,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -3930,9 +3926,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -3954,9 +3950,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920</f>
@@ -3978,9 +3974,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4">
         <f>458+115+189</f>
@@ -4002,9 +3998,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -4026,9 +4022,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4">
         <f>7985+1084+1117</f>
@@ -4050,9 +4046,9 @@
       <c r="H18"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4">
         <f>2592+518+820</f>
@@ -4074,9 +4070,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365-3314.616</f>
@@ -4098,7 +4094,7 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21"/>
       <c r="B21" s="4"/>
       <c r="D21"/>
@@ -4108,7 +4104,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22">
@@ -4133,20 +4129,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4155,11 +4151,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4179,13 +4175,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -4207,9 +4203,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -4231,9 +4227,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -4255,9 +4251,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -4279,9 +4275,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -4303,9 +4299,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4">
         <v>52890</v>
@@ -4326,9 +4322,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(410+205+135+181)*2</f>
@@ -4350,9 +4346,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -4374,9 +4370,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -4398,9 +4394,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -4422,9 +4418,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920</f>
@@ -4446,9 +4442,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4">
         <f>458+115+189</f>
@@ -4470,9 +4466,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -4494,9 +4490,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4">
         <f>7985+1084+1117+2249</f>
@@ -4515,14 +4511,14 @@
       </c>
       <c r="F18"/>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H18"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4">
         <f>2592+518+820</f>
@@ -4544,9 +4540,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365-3314.616-1057.21</f>
@@ -4565,12 +4561,12 @@
       </c>
       <c r="F20"/>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21"/>
       <c r="B21" s="4"/>
       <c r="D21"/>
@@ -4580,7 +4576,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22">
@@ -4605,20 +4601,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4627,11 +4623,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4651,13 +4647,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -4679,9 +4675,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -4703,9 +4699,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -4727,9 +4723,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>130+126+33+57+173+130</f>
@@ -4751,9 +4747,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -4775,9 +4771,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4">
         <v>52890</v>
@@ -4798,9 +4794,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(410+205+135+181)*2</f>
@@ -4822,9 +4818,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -4846,9 +4842,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -4870,9 +4866,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -4894,9 +4890,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920-438</f>
@@ -4915,14 +4911,14 @@
       </c>
       <c r="F15"/>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4">
         <f>458+115+189</f>
@@ -4944,9 +4940,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -4968,9 +4964,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4">
         <f>7985+1084+1117+2249</f>
@@ -4992,9 +4988,9 @@
       <c r="H18"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4">
         <f>2592+518+820</f>
@@ -5016,9 +5012,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365-3314.616-1057.21+565.427</f>
@@ -5037,12 +5033,12 @@
       </c>
       <c r="F20"/>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21"/>
       <c r="B21" s="4"/>
       <c r="D21"/>
@@ -5052,7 +5048,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22">
@@ -5077,20 +5073,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5099,11 +5095,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5123,13 +5119,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -5151,9 +5147,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -5175,9 +5171,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4">
         <v>1410</v>
@@ -5195,14 +5191,14 @@
       </c>
       <c r="F7"/>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -5224,9 +5220,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -5248,9 +5244,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -5272,9 +5268,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4">
         <v>52890</v>
@@ -5295,9 +5291,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4">
         <f>(410+205+135+181)*2</f>
@@ -5319,9 +5315,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -5343,9 +5339,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -5367,9 +5363,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -5391,9 +5387,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920-438</f>
@@ -5415,9 +5411,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -5439,9 +5435,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -5463,9 +5459,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249</f>
@@ -5487,9 +5483,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -5511,9 +5507,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365-3314.616-1057.21+565.427-1288.599</f>
@@ -5532,12 +5528,12 @@
       </c>
       <c r="F21"/>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -5547,7 +5543,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -5572,19 +5568,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5593,11 +5589,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5617,13 +5613,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -5641,9 +5637,9 @@
         <v>8.5589427494721843E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -5661,9 +5657,9 @@
         <v>4.30336230611119E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -5681,9 +5677,9 @@
         <v>3.898820994803788E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -5701,9 +5697,9 @@
         <v>4.2054883552400495E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>862+390+71+35-217-171</f>
@@ -5721,9 +5717,9 @@
         <v>1.8464597367757223E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205</f>
@@ -5741,9 +5737,9 @@
         <v>5.8589073869135075E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -5761,9 +5757,9 @@
         <v>0.12295609088681428</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317</f>
@@ -5781,9 +5777,9 @@
         <v>6.7871346708025457E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -5801,12 +5797,12 @@
         <v>3.8830453355036113E-2</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205</f>
@@ -5824,9 +5820,9 @@
         <v>0.2178785888012541</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -5844,9 +5840,9 @@
         <v>4.0812363479593008E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459</f>
@@ -5864,9 +5860,9 @@
         <v>3.6162755882797E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -5884,9 +5880,9 @@
         <v>6.2118996097145905E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -5904,9 +5900,9 @@
         <v>6.3128066527372573E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>48.4+47.4+129.5-97.5-56+86.5+391.64-150.9-44.65+28+666.65-157.4-303.27+183.51-105.34-76.3-98.36+434.72-160.72-64.6+155.95-254.77-161.7-85.65+146.4+135.27+113.1+214.6+13.78-151.45-147.34-70.81-58.76-273.8+189.4+55.07+264.7-276.6-84.36-112.97+24.27-110.22+137.37-247.49+1021.8-192.05+26.325-177.03-179.14-89.792-89.088-97.856+450.59-71.562+397.578+397.301-75.02-22.928-200.46-205.68-43.938-31.811-49.14-46.569-29.16+738.808-401.23-100.49-99.71-232.613+258.656-266.108-170.465+41.913+196.7+377.35+208.038+121.878+28.182-485.27-322.169+668.43-158.668-57.284+224.7-117.369-198.275-129.083-462.433-72.875-123.419-244.78+94.074+103.702-224.999+35.566+48.391-39.24+160.338-155.174+25.14+418.03-263.255-189.24-0.584-4.192-1.638+4.995+35.895+3.597+114.35+45.302-120.94-80.7+72.904-84.743-26.744+218.983-75.256-142.851+0.253+69.61-71.167+30.957+222.439+188.91+72.355-184.538-32.16-119.837-173.096-3.667+2.8606-4.408-0.094+816.414-40.951+314.853-902.092-187.971+1089.576-388.495+905.333-1333.44+246.344+2.976-310+1092.909-498.03+1348.808-852.799-961.499+2.927-60.272-173.975-41.354+10.883-16.86+1119.46-1181.99+37.038+73.378+352.797+997.672-308.837+443.467+711.919+1282.768-2276.683-538.214-548.973+632.774+151.229-61.672+2709.092-582.471-1043.373+1196.928+295.009-904.847+20.192+376.16</f>
@@ -5924,14 +5920,14 @@
         <v>6.3521522968797095E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -5947,19 +5943,19 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C18A242-0910-4E92-A461-DA397E54CBAB}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>2640000</v>
@@ -5969,9 +5965,9 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="B4">
         <v>3470000</v>
@@ -5981,9 +5977,9 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>3470000</v>
@@ -5993,9 +5989,9 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="B6">
         <v>5029000</v>
@@ -6005,9 +6001,9 @@
         <v>10058</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="B7">
         <v>4335000</v>
@@ -6017,9 +6013,9 @@
         <v>8670</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="B8">
         <v>4335000</v>
@@ -6029,9 +6025,9 @@
         <v>8670</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B9">
         <v>5073000</v>
@@ -6041,9 +6037,9 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B10">
         <v>5073000</v>
@@ -6053,9 +6049,9 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="B11">
         <v>5073000</v>
@@ -6065,9 +6061,9 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="B12">
         <v>4016000</v>
@@ -6077,9 +6073,9 @@
         <v>8032</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="B13">
         <v>4016000</v>
@@ -6089,9 +6085,9 @@
         <v>8032</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="B14">
         <v>3292000</v>
@@ -6101,7 +6097,7 @@
         <v>6584</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="C16" s="2">
         <f>SUM(C3:C15)</f>
         <v>99644</v>
@@ -6119,20 +6115,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6141,11 +6137,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6165,13 +6161,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -6193,9 +6189,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4">
         <f>448*2</f>
@@ -6217,9 +6213,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4">
         <v>1410</v>
@@ -6240,9 +6236,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -6264,9 +6260,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -6288,9 +6284,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365</f>
@@ -6312,9 +6308,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4">
         <v>52890</v>
@@ -6335,9 +6331,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4">
         <f>(410+205+135+181)*2</f>
@@ -6359,9 +6355,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -6383,9 +6379,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -6407,9 +6403,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -6431,9 +6427,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850-1323-920-438</f>
@@ -6455,9 +6451,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -6479,9 +6475,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -6503,9 +6499,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249</f>
@@ -6527,9 +6523,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -6551,9 +6547,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898-939.595-845.343+2113.889+1938.365-3314.616-1057.21+565.427-1288.599+99.644</f>
@@ -6577,7 +6573,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -6587,7 +6583,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -6609,7 +6605,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270A1E4-8160-48C8-BABC-214DD704FB6A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6621,19 +6617,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6642,11 +6638,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6666,13 +6662,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -6690,9 +6686,9 @@
         <v>8.2550487155592073E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -6710,9 +6706,9 @@
         <v>4.2540533790381356E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -6730,9 +6726,9 @@
         <v>4.0790763649065677E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -6750,9 +6746,9 @@
         <v>4.2863348347739236E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>862+390+71+35-217-171-970</f>
@@ -6770,12 +6766,12 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>410+205</f>
@@ -6793,9 +6789,9 @@
         <v>5.9639153231055786E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -6813,9 +6809,9 @@
         <v>0.12333196970946313</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317</f>
@@ -6833,9 +6829,9 @@
         <v>7.0765821141005478E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -6853,9 +6849,9 @@
         <v>3.8637479919850753E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>10500+5250-3258-1143-1205-2468</f>
@@ -6873,12 +6869,12 @@
         <v>0.16488889176113741</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>458+115+189</f>
@@ -6896,9 +6892,9 @@
         <v>4.0297149082502502E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>3075+1537+1153-53-1428-925-484-459</f>
@@ -6916,9 +6912,9 @@
         <v>3.5186145616983341E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -6936,9 +6932,9 @@
         <v>6.1664787591403099E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -6956,9 +6952,9 @@
         <v>6.2005386988537491E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>48.4+47.4+129.5-97.5-56+86.5+391.64-150.9-44.65+28+666.65-157.4-303.27+183.51-105.34-76.3-98.36+434.72-160.72-64.6+155.95-254.77-161.7-85.65+146.4+135.27+113.1+214.6+13.78-151.45-147.34-70.81-58.76-273.8+189.4+55.07+264.7-276.6-84.36-112.97+24.27-110.22+137.37-247.49+1021.8-192.05+26.325-177.03-179.14-89.792-89.088-97.856+450.59-71.562+397.578+397.301-75.02-22.928-200.46-205.68-43.938-31.811-49.14-46.569-29.16+738.808-401.23-100.49-99.71-232.613+258.656-266.108-170.465+41.913+196.7+377.35+208.038+121.878+28.182-485.27-322.169+668.43-158.668-57.284+224.7-117.369-198.275-129.083-462.433-72.875-123.419-244.78+94.074+103.702-224.999+35.566+48.391-39.24+160.338-155.174+25.14+418.03-263.255-189.24-0.584-4.192-1.638+4.995+35.895+3.597+114.35+45.302-120.94-80.7+72.904-84.743-26.744+218.983-75.256-142.851+0.253+69.61-71.167+30.957+222.439+188.91+72.355-184.538-32.16-119.837-173.096-3.667+2.8606-4.408-0.094+816.414-40.951+314.853-902.092-187.971+1089.576-388.495+905.333-1333.44+246.344+2.976-310+1092.909-498.03+1348.808-852.799-961.499+2.927-60.272-173.975-41.354+10.883-16.86+1119.46-1181.99+37.038+73.378+352.797+997.672-308.837+443.467+711.919+1282.768-2276.683-538.214-548.973+632.774+151.229-61.672+2709.092-582.471-1043.373+1196.928+295.009-904.847+20.192+376.16+3566.46</f>
@@ -6976,14 +6972,14 @@
         <v>0.1348380820152828</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7002,19 +6998,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7023,11 +7019,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7047,13 +7043,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -7071,9 +7067,9 @@
         <v>7.4325611977889366E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -7091,9 +7087,9 @@
         <v>4.3902081139617417E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -7111,9 +7107,9 @@
         <v>3.7920624473030441E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -7131,9 +7127,9 @@
         <v>4.3786803249533539E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <f>410+205</f>
@@ -7151,9 +7147,9 @@
         <v>6.5212308735013005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -7171,9 +7167,9 @@
         <v>0.1161015519574472</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <f>13763+6317</f>
@@ -7191,9 +7187,9 @@
         <v>7.373508382464701E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -7211,9 +7207,9 @@
         <v>3.8039109800291827E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>10500+5250-3258-1143-1205-2468</f>
@@ -7231,9 +7227,9 @@
         <v>0.16715718123326509</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <f>458+115+189</f>
@@ -7251,9 +7247,9 @@
         <v>4.6534733584497653E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467</f>
@@ -7271,12 +7267,12 @@
         <v>2.8921490006447597E-2</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <f>7985+1084</f>
@@ -7294,9 +7290,9 @@
         <v>6.2970166262901778E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -7314,9 +7310,9 @@
         <v>6.2861212319826151E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <f>48.4+47.4+129.5-97.5-56+86.5+391.64-150.9-44.65+28+666.65-157.4-303.27+183.51-105.34-76.3-98.36+434.72-160.72-64.6+155.95-254.77-161.7-85.65+146.4+135.27+113.1+214.6+13.78-151.45-147.34-70.81-58.76-273.8+189.4+55.07+264.7-276.6-84.36-112.97+24.27-110.22+137.37-247.49+1021.8-192.05+26.325-177.03-179.14-89.792-89.088-97.856+450.59-71.562+397.578+397.301-75.02-22.928-200.46-205.68-43.938-31.811-49.14-46.569-29.16+738.808-401.23-100.49-99.71-232.613+258.656-266.108-170.465+41.913+196.7+377.35+208.038+121.878+28.182-485.27-322.169+668.43-158.668-57.284+224.7-117.369-198.275-129.083-462.433-72.875-123.419-244.78+94.074+103.702-224.999+35.566+48.391-39.24+160.338-155.174+25.14+418.03-263.255-189.24-0.584-4.192-1.638+4.995+35.895+3.597+114.35+45.302-120.94-80.7+72.904-84.743-26.744+218.983-75.256-142.851+0.253+69.61-71.167+30.957+222.439+188.91+72.355-184.538-32.16-119.837-173.096-3.667+2.8606-4.408-0.094+816.414-40.951+314.853-902.092-187.971+1089.576-388.495+905.333-1333.44+246.344+2.976-310+1092.909-498.03+1348.808-852.799-961.499+2.927-60.272-173.975-41.354+10.883-16.86+1119.46-1181.99+37.038+73.378+352.797+997.672-308.837+443.467+711.919+1282.768-2276.683-538.214-548.973+632.774+151.229-61.672+2709.092-582.471-1043.373+1196.928+295.009-904.847+20.192+376.16+3566.46+349.386</f>
@@ -7334,14 +7330,14 @@
         <v>0.13853204143559189</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -7360,19 +7356,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7381,11 +7377,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7405,13 +7401,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -7429,9 +7425,9 @@
         <v>8.7777300334744582E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -7449,9 +7445,9 @@
         <v>4.292043278796516E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -7469,9 +7465,9 @@
         <v>3.5388382817319451E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -7489,9 +7485,9 @@
         <v>4.2174519665264087E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <f>410+205</f>
@@ -7509,9 +7505,9 @@
         <v>6.4882510618103129E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -7529,9 +7525,9 @@
         <v>0.11317869205175127</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <f>13763+6317+2811</f>
@@ -7549,12 +7545,12 @@
         <v>7.9947024411621728E-2</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -7572,9 +7568,9 @@
         <v>3.5254076666252271E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>10500+5250-3258-1143-1205-2468</f>
@@ -7592,9 +7588,9 @@
         <v>0.15813140575555054</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <f>458+115+189</f>
@@ -7612,9 +7608,9 @@
         <v>4.9976908004650142E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467</f>
@@ -7632,9 +7628,9 @@
         <v>2.7920094352735934E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <f>7985+1084</f>
@@ -7652,9 +7648,9 @@
         <v>6.606592913684424E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -7672,9 +7668,9 @@
         <v>6.6465828487578829E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <f>6932.14-496.76</f>
@@ -7692,14 +7688,14 @@
         <v>0.12991689490961872</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -7718,19 +7714,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7739,11 +7735,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7763,13 +7759,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -7787,9 +7783,9 @@
         <v>8.9551033645904457E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -7807,9 +7803,9 @@
         <v>4.5161177827461652E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -7827,9 +7823,9 @@
         <v>3.617761024607747E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -7847,9 +7843,9 @@
         <v>4.3478639795403791E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <f>410+205</f>
@@ -7867,9 +7863,9 @@
         <v>6.7244234840522651E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -7887,9 +7883,9 @@
         <v>0.10147634848955221</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <f>13763+6317+2811+3464</f>
@@ -7907,12 +7903,12 @@
         <v>9.0135561540290163E-2</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -7930,9 +7926,9 @@
         <v>3.4349354668258857E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>10500+5250-3258-1143-1205-2468</f>
@@ -7950,9 +7946,9 @@
         <v>0.15750619994813211</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <f>458+115+189</f>
@@ -7970,9 +7966,9 @@
         <v>5.4645652229266727E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45</f>
@@ -7990,12 +7986,12 @@
         <v>2.517994595110129E-2</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <f>7985+1084</f>
@@ -8013,9 +8009,9 @@
         <v>6.7000812855064013E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -8033,9 +8029,9 @@
         <v>6.6696128382538203E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <f>6932.14-496.76-518.245</f>
@@ -8053,14 +8049,14 @@
         <v>0.1213972995804265</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -8079,20 +8075,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8101,11 +8097,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8125,13 +8121,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -8149,9 +8145,9 @@
         <v>8.9936210741027575E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -8169,9 +8165,9 @@
         <v>4.8358319369282705E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -8189,9 +8185,9 @@
         <v>3.9260058413279932E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -8209,9 +8205,9 @@
         <v>4.6382328638636297E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <f>410+205+135</f>
@@ -8229,12 +8225,12 @@
         <v>7.9492838208315111E-2</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -8252,9 +8248,9 @@
         <v>8.898566120108474E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -8272,12 +8268,12 @@
         <v>9.2186317207099577E-2</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -8295,9 +8291,9 @@
         <v>3.7115459742868846E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>10500+5250-3258-1143-1205-2468</f>
@@ -8315,9 +8311,9 @@
         <v>0.14824431943788036</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <f>458+115+189</f>
@@ -8335,9 +8331,9 @@
         <v>5.6522359900976551E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -8355,12 +8351,12 @@
         <v>4.9416978281795719E-2</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <f>7985+1084+1117</f>
@@ -8378,13 +8374,13 @@
         <v>7.2157566578979468E-2</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -8402,9 +8398,9 @@
         <v>7.6847346161371441E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <f>6932.14-496.76-518.245-2447.575</f>
@@ -8422,14 +8418,14 @@
         <v>7.5094236117401791E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -8448,20 +8444,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8470,11 +8466,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8494,13 +8490,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -8518,9 +8514,9 @@
         <v>9.3674560616357413E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -8538,9 +8534,9 @@
         <v>4.3258536229745813E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -8558,9 +8554,9 @@
         <v>3.4267334212357746E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -8578,9 +8574,9 @@
         <v>4.6255339857041895E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <f>410+205+135</f>
@@ -8598,9 +8594,9 @@
         <v>7.7347464975350583E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -8618,9 +8614,9 @@
         <v>8.2129080093727658E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -8638,9 +8634,9 @@
         <v>0.11391786325167595</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -8658,9 +8654,9 @@
         <v>3.3989275082864992E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535</f>
@@ -8678,12 +8674,12 @@
         <v>0.1196048324646419</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <f>458+115+189</f>
@@ -8701,9 +8697,9 @@
         <v>6.2294756278518729E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -8721,9 +8717,9 @@
         <v>4.6249219585758651E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <f>7985+1084+1117</f>
@@ -8742,9 +8738,9 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -8762,9 +8758,9 @@
         <v>7.865372085735603E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683</f>
@@ -8782,14 +8778,14 @@
         <v>9.8607501231335742E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -8808,20 +8804,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8830,11 +8826,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8854,13 +8850,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -8878,9 +8874,9 @@
         <v>9.5069916719442413E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -8898,9 +8894,9 @@
         <v>4.5186744589375868E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>130+126+33+57+173+130</f>
@@ -8918,9 +8914,9 @@
         <v>3.0450323604915442E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300</f>
@@ -8938,9 +8934,9 @@
         <v>4.2466281782186456E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <f>410+205+135</f>
@@ -8958,9 +8954,9 @@
         <v>6.9549357355978406E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <f>(1875+937+309+619)*2</f>
@@ -8978,9 +8974,9 @@
         <v>8.0355366029198974E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -8998,9 +8994,9 @@
         <v>0.11014903241534946</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <f>480+154+159+192-246-74-85-96</f>
@@ -9018,9 +9014,9 @@
         <v>3.4049056695486642E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>10500+5250-3258-1143-1205-2468-1535-850</f>
@@ -9038,12 +9034,12 @@
         <v>0.11985796416363112</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <f>458+115+189</f>
@@ -9061,9 +9057,9 @@
         <v>7.0655028250866142E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>3075+1537+1153-53-1428-925-484-459-467-45+2345</f>
@@ -9081,9 +9077,9 @@
         <v>4.3545829773746762E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <f>7985+1084+1117</f>
@@ -9102,9 +9098,9 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -9122,9 +9118,9 @@
         <v>6.9564267646268996E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <f>6932.14-496.76-518.245-2447.575+1559.683+1090.898</f>
@@ -9142,14 +9138,14 @@
         <v>0.11435222923483881</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
